--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jun-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jun-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>9259175.24</v>
+        <v>10249.43</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5880061.74</v>
+        <v>6508.93</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>7769034</v>
+        <v>8599.92</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>29100184.35</v>
+        <v>32212.41</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8811033</v>
+        <v>9753.360000000001</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>18703282.36</v>
+        <v>20703.57</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>9550146.949999999</v>
+        <v>10571.52</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5525000</v>
+        <v>6115.89</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>14252238</v>
+        <v>15776.5</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>10743402.88</v>
+        <v>11892.39</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>11747085.56</v>
+        <v>13003.42</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>13300457.1</v>
+        <v>14722.92</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>20189523</v>
+        <v>22348.76</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>9209542.6</v>
+        <v>10194.49</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6897534</v>
+        <v>7635.22</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>47992202.3</v>
+        <v>53124.9</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6473017.6</v>
+        <v>7165.3</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>9717269.380000001</v>
+        <v>10756.52</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>7996059.12</v>
+        <v>8851.23</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>9191539.560000001</v>
+        <v>10174.56</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>5957300.44</v>
+        <v>6594.43</v>
       </c>
     </row>
     <row r="23">
@@ -1846,11 +1846,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>15617752.1</v>
+        <v>17288.05</v>
       </c>
     </row>
     <row r="24">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>13284315.1</v>
+        <v>14705.05</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8982876</v>
+        <v>9943.58</v>
       </c>
     </row>
     <row r="26">
@@ -2029,11 +2029,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>6583550.05</v>
+        <v>7287.65</v>
       </c>
     </row>
     <row r="27">
@@ -2090,11 +2090,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>42840000</v>
+        <v>47421.68</v>
       </c>
     </row>
     <row r="28">
@@ -2151,11 +2151,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5166752.2</v>
+        <v>5719.33</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>15519806</v>
+        <v>17179.63</v>
       </c>
     </row>
     <row r="30">
@@ -2273,11 +2273,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>52335010</v>
+        <v>57932.17</v>
       </c>
     </row>
     <row r="31">
@@ -2334,17 +2334,17 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>9435340.039999999</v>
+        <v>10444.44</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1261592-594-CM26</t>
+          <t>1180968-34-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2364,48 +2364,48 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cancelada por Comprador</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>43754664.6</v>
+        <v>33402.17</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1180968-34-CM26</t>
+          <t>1499887-471-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2430,43 +2430,43 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>Servicio Nacional de Reinserción Social Juvenil</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>30175000</v>
+        <v>8327.690000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1499887-471-CM26</t>
+          <t>1499887-473-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2517,17 +2517,17 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>7523101.32</v>
+        <v>19161.82</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1499887-473-CM26</t>
+          <t>2760-71-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2552,43 +2552,43 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.151.200-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>17310491.66</v>
+        <v>8386.389999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2760-71-CM26</t>
+          <t>5647-107-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,43 +2613,43 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7576135</v>
+        <v>15232.96</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5647-107-CM26</t>
+          <t>3500-135-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2674,43 +2674,43 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.081.700-4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE QUINTA DE TILCOCO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>13761221.2</v>
+        <v>11472.23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3500-135-CM26</t>
+          <t>2291-1118-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2735,43 +2735,43 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.081.700-4</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTA DE TILCOCO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>10363829</v>
+        <v>11105.81</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2291-1118-CM26</t>
+          <t>1057922-25-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2796,43 +2796,43 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>10032816</v>
+        <v>7613.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1057922-25-CM26</t>
+          <t>2585-386-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2852,48 +2852,48 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>6878279.86</v>
+        <v>35795.41</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2585-386-CM26</t>
+          <t>5520-3737-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2918,43 +2918,43 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>32337011.55</v>
+        <v>6770.76</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5520-3737-CM26</t>
+          <t>1233615-938-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,43 +2979,43 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.043.435-1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>6116594.9</v>
+        <v>51556.72</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1233615-938-CM26</t>
+          <t>1175-521-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3040,43 +3040,43 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.043.435-1</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>46575529</v>
+        <v>13616.04</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1175-521-CM26</t>
+          <t>2727-512-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3096,48 +3096,48 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.607.400-8</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>12300520</v>
+        <v>11406.98</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2727-512-CM26</t>
+          <t>1079650-57-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,43 +3162,43 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>92.999.000-5</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>10304887.18</v>
+        <v>10063.67</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1079650-57-CM26</t>
+          <t>4629-150-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3218,48 +3218,48 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>9091362</v>
+        <v>6593.48</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4629-150-CM26</t>
+          <t>859378-380-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3279,22 +3279,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3310,17 +3310,17 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>5956449.8</v>
+        <v>6593.48</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>859378-380-CM26</t>
+          <t>1057049-16088-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,53 +3335,53 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>5956449.8</v>
+        <v>7418.86</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1057049-16088-CM26</t>
+          <t>2385-473-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3406,43 +3406,43 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>6702077.45</v>
+        <v>8675.540000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2385-473-CM26</t>
+          <t>4201-381-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,43 +3467,43 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.073.900-3</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE CURACAVI</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>IMPORTADORA FULLMUEBLES SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.351.814-9</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>7837344.2</v>
+        <v>10805.3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4201-381-CM26</t>
+          <t>1232565-182-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3523,48 +3523,48 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.073.900-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAVI</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>IMPORTADORA FULLMUEBLES SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>77.351.814-9</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>9761340.5</v>
+        <v>6593.48</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1232565-182-CM26</t>
+          <t>5586-1964-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,43 +3589,43 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>INDUMAC LTDA.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>83.732.700-8</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>5956449.8</v>
+        <v>153194.57</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5586-1964-CM26</t>
+          <t>2178-186-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3645,48 +3645,48 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>INDUMAC LTDA.</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>83.732.700-8</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>138393570.48</v>
+        <v>22291.54</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2178-186-CM26</t>
+          <t>4794-75-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3706,103 +3706,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.719.470-6</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>20137824</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>4794-75-CM26</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2239-4-LR25</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>60.910.000-1</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>UNIVERSIDAD DE CHILE</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>INTERGROUPE S.A.</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>76.719.470-6</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="n">
-        <v>13552853.05</v>
+        <v>15002.31</v>
       </c>
     </row>
   </sheetData>
